--- a/public/gabarit-import-apprenants.xlsx
+++ b/public/gabarit-import-apprenants.xlsx
@@ -75,6 +75,7 @@
     <col min="21" max="21" width="30" customWidth="1"/>
     <col min="22" max="22" width="32" customWidth="1"/>
     <col min="23" max="23" width="22" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -191,6 +192,11 @@
       <c r="W1" t="inlineStr">
         <is>
           <t xml:space="preserve">Genre (obligatoire)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes médicales</t>
         </is>
       </c>
     </row>
@@ -628,23 +634,40 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Une ligne par ENFANT.</t>
-        </is>
-      </c>
-    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes médicales</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texte libre</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Une famille de trois enfants occupe donc trois lignes, avec les mêmes colonnes de tuteurs répétées.</t>
+          <t xml:space="preserve">Une ligne par ENFANT.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Une famille de trois enfants occupe donc trois lignes, avec les mêmes colonnes de tuteurs répétées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t xml:space="preserve">Une cellule laissée vide ne supprime jamais une information déjà enregistrée.</t>
         </is>
